--- a/artfynd/A 13755-2026 artfynd.xlsx
+++ b/artfynd/A 13755-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126211198</v>
+        <v>126215699</v>
       </c>
       <c r="B2" t="n">
-        <v>100450</v>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596563</v>
+        <v>596568</v>
       </c>
       <c r="R2" t="n">
-        <v>6554693</v>
+        <v>6554728</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126211232</v>
+        <v>126216420</v>
       </c>
       <c r="B3" t="n">
-        <v>100543</v>
+        <v>102560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>222133</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596563</v>
+        <v>596534</v>
       </c>
       <c r="R3" t="n">
-        <v>6554693</v>
+        <v>6554650</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,9 +869,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Skogsbryn mot åkermark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126215699</v>
+        <v>126211232</v>
       </c>
       <c r="B4" t="n">
-        <v>98398</v>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219875</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596568</v>
+        <v>596563</v>
       </c>
       <c r="R4" t="n">
-        <v>6554728</v>
+        <v>6554693</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,6 +993,216 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126211198</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grindatorp N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>596563</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6554693</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126210470</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105053</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223871</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig åkerrättika</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Raphanus raphanistrum subsp. raphanistrum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grindatorp N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>596591</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6554740</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Åkermark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13755-2026 artfynd.xlsx
+++ b/artfynd/A 13755-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126215699</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126216420</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126211232</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126211198</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,8 +1228,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126210470</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>